--- a/technology_surveys/019_digital_inclusion_in_care_delivery_survey--technology_surveys.xlsx
+++ b/technology_surveys/019_digital_inclusion_in_care_delivery_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -538,20 +538,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>clinician_device_access_hospital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Device Access in the Hospital</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select how often you access devices while providing care in the hospital</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,22 +570,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>clinician_device_access_1</t>
+          <t>clinician_device_access_home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Device Access in the Hospital</t>
+          <t>Device Access in the Home</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Please select how often you access devices while providing care in the hospital</t>
+          <t>Please select how often you access devices while providing care in the home</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -593,22 +597,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>clinician_device_access_2</t>
+          <t>clinician_comfort_with_technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Device Access in the Home</t>
+          <t>Comfort with Technology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Please select how often you access devices while providing care in the home</t>
+          <t>Please select how comfortable you feel when using technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -620,44 +624,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>clinician_comfort_with_tools_1</t>
+          <t>clinician_barriers_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Comfort with Technology</t>
+          <t>Barriers to Technology Use</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Please select how comfortable you feel when using technology</t>
+          <t>Please select the main barrier you face when using technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>clinician_barriers_1</t>
+          <t>clinician_other_barriers_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Barriers to Technology Use</t>
+          <t>Other Barriers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Please select the main barrier you face when using technology</t>
+          <t>Please provide any other barriers you face when using technology</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -669,167 +673,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>clinician_barriers_2</t>
+          <t>clinician_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Barriers to Technology Use</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Please select the main barrier you face when using technology</t>
+          <t>Please provide any comments or additional information</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>clinician_other_barriers_1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Other Barriers</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>clinician_other_barriers_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Other Barriers</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>clinician_other_barriers_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Other Barriers</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>clinician_other_barriers_4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Other Barriers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>clinician_other_barriers_5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Other Barriers</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>clinician_comments</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Please provide any comments or additional information</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -846,12 +708,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,204 +736,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clinician_device_access_1_choices</t>
+          <t>clinician_device_access_hospital_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very often'}</t>
+          <t>Very often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>clinician_device_access_1_choices</t>
+          <t>clinician_device_access_hospital_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_often'}</t>
+          <t>somewhat_often</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat often'}</t>
+          <t>Somewhat often</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>clinician_device_access_1_choices</t>
+          <t>clinician_device_access_hospital_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>clinician_device_access_1_choices</t>
+          <t>clinician_device_access_hospital_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>clinician_device_access_2_choices</t>
+          <t>clinician_device_access_home_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very often'}</t>
+          <t>Very often</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>clinician_device_access_2_choices</t>
+          <t>clinician_device_access_home_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_often'}</t>
+          <t>somewhat_often</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat often'}</t>
+          <t>Somewhat often</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>clinician_device_access_2_choices</t>
+          <t>clinician_device_access_home_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>clinician_device_access_2_choices</t>
+          <t>clinician_device_access_home_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clinician_comfort_with_tools_1_choices</t>
+          <t>clinician_comfort_with_technology_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'very_comfortable'}</t>
+          <t>very_comfortable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Very comfortable'}</t>
+          <t>Very comfortable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clinician_comfort_with_tools_1_choices</t>
+          <t>clinician_comfort_with_technology_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_comfortable'}</t>
+          <t>somewhat_comfortable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat comfortable'}</t>
+          <t>Somewhat comfortable</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clinician_comfort_with_tools_1_choices</t>
+          <t>clinician_comfort_with_technology_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_comfortable'}</t>
+          <t>not_very_comfortable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not very comfortable'}</t>
+          <t>Not very comfortable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clinician_comfort_with_tools_1_choices</t>
+          <t>clinician_comfort_with_technology_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_comfortable'}</t>
+          <t>not_at_all_comfortable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all comfortable'}</t>
+          <t>Not at all comfortable</t>
         </is>
       </c>
     </row>
@@ -1083,12 +945,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'technical_difficulties'}</t>
+          <t>technical_difficulties</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Technical difficulties'}</t>
+          <t>Technical difficulties</t>
         </is>
       </c>
     </row>
@@ -1100,12 +962,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_training'}</t>
+          <t>lack_of_training</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of training'}</t>
+          <t>Lack of training</t>
         </is>
       </c>
     </row>
@@ -1117,12 +979,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'fear_of_data_security_risks'}</t>
+          <t>fear_of_data_security_risks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Fear of data security risks'}</t>
+          <t>Fear of data security risks</t>
         </is>
       </c>
     </row>
@@ -1134,80 +996,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>clinician_barriers_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'label':_'technical_difficulties'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'label': 'Technical difficulties'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>clinician_barriers_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'lack_of_training'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'Lack of training'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>clinician_barriers_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'label':_'fear_of_data_security_risks'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'label': 'Fear of data security risks'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>clinician_barriers_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
